--- a/results/naturverbundenheit/observables/nature-dataset-distance-matrix-jensenshannon-auto.xlsx
+++ b/results/naturverbundenheit/observables/nature-dataset-distance-matrix-jensenshannon-auto.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ43"/>
+  <dimension ref="A1:AJ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,205 +441,170 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>France</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>India</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>United States of America</t>
         </is>
@@ -655,5579 +620,3913 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3996095660459038</v>
+        <v>0.2086038477508078</v>
       </c>
       <c r="D2" t="n">
-        <v>0.243935177697056</v>
+        <v>0.1784079730005889</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1666474632714857</v>
+        <v>0.2819885678330677</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2965189453783977</v>
+        <v>0.357957190830154</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3636747830766739</v>
+        <v>0.3289563846085855</v>
       </c>
       <c r="H2" t="n">
-        <v>0.438287842693098</v>
+        <v>0.3918216004813274</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3545868537848112</v>
+        <v>0.4463351066470099</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3352985487834386</v>
+        <v>0.3446252878661659</v>
       </c>
       <c r="K2" t="n">
-        <v>0.375576582308957</v>
+        <v>0.3220565418753426</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3963325722961649</v>
+        <v>0.3422107334198201</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2611821056023608</v>
+        <v>0.2551825683450369</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2833457778512003</v>
+        <v>0.3369423203761147</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2849203707821831</v>
+        <v>0.3413139521876343</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2611925164018816</v>
+        <v>0.3379547227235137</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2438531203230072</v>
+        <v>0.4022916873690882</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3350891621522544</v>
+        <v>0.4702634547527632</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3461741770942514</v>
+        <v>0.3778380270460248</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3402511101860129</v>
+        <v>0.4820229033299572</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4298678384060649</v>
+        <v>0.45224383602069</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6679247697882829</v>
+        <v>0.4015146923735201</v>
       </c>
       <c r="W2" t="n">
-        <v>0.435371867393919</v>
+        <v>0.3033241053052645</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3759831064158954</v>
+        <v>0.2189810046139109</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.534711486614373</v>
+        <v>0.4127816246583579</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.4383084249162878</v>
+        <v>0.4659747179501191</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.4132117330767075</v>
+        <v>0.314116613831922</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2715240855395805</v>
+        <v>0.3235847926971672</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1611444284299403</v>
+        <v>0.1861819481701183</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3382980497797735</v>
+        <v>0.3620940229625715</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3774793359873343</v>
+        <v>0.3046194617413157</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2869246775107943</v>
+        <v>0.1565094563156229</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3136262933685272</v>
+        <v>0.4566797376786071</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.216139547794732</v>
+        <v>0.3388028580878903</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2193068745582441</v>
+        <v>0.2500640977011001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2858124149065213</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.1599345305495599</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.7812048733065775</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.5014959369649594</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.3657642261553331</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.4281790522358774</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.2600279882612592</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.2196147769685995</v>
+        <v>0.2054683227824581</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3996095660459038</v>
+        <v>0.2086038477508078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3812664332066983</v>
+        <v>0.2117802071983159</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2913034928944097</v>
+        <v>0.3099645092875766</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2596380329829508</v>
+        <v>0.2754829345478712</v>
       </c>
       <c r="G3" t="n">
-        <v>0.252321103760753</v>
+        <v>0.1947039802039447</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4894442588983932</v>
+        <v>0.2946439565084543</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3250731689920256</v>
+        <v>0.304493895682044</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3661683188435101</v>
+        <v>0.2723004253443609</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2640095521711325</v>
+        <v>0.3638787036627291</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3878952776785592</v>
+        <v>0.3191261707614903</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2974565459129302</v>
+        <v>0.2583035212512218</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3027753782939155</v>
+        <v>0.3908331283267535</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2003139282020396</v>
+        <v>0.2930797335697531</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2085398669304941</v>
+        <v>0.237238249223889</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2912905338157356</v>
+        <v>0.4027614882947793</v>
       </c>
       <c r="R3" t="n">
-        <v>0.268584286460668</v>
+        <v>0.4192985205160406</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3190999396781072</v>
+        <v>0.3438310488166891</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3269628209310923</v>
+        <v>0.3696217902733633</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1913193787943113</v>
+        <v>0.4152538522828616</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6317544851546755</v>
+        <v>0.3206642101259284</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1854963280241858</v>
+        <v>0.3248114595238429</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1759476038430624</v>
+        <v>0.2152302121219773</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.557609006176916</v>
+        <v>0.4513670273423105</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2982861175313762</v>
+        <v>0.4625161201541372</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2527916233891053</v>
+        <v>0.3182811295439305</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2945398534646176</v>
+        <v>0.3356637897293322</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3123404618789838</v>
+        <v>0.2321450678231125</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3406378610909753</v>
+        <v>0.3679654603517222</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3448637947831505</v>
+        <v>0.2676977291597868</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2169808890681555</v>
+        <v>0.2580213922664524</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.2878997214712728</v>
+        <v>0.4681113610637689</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.3406959276128624</v>
+        <v>0.3375205849514797</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.2539300538288434</v>
+        <v>0.3010666876846366</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.2594059147514446</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.3367235115124469</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0.6961803443665078</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.3933408718232482</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.3664967466749209</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.3101215835059233</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.2353246010605236</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.3070745460078571</v>
+        <v>0.2901962612063297</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.243935177697056</v>
+        <v>0.1784079730005889</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3812664332066983</v>
+        <v>0.2117802071983159</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2575033781905981</v>
+        <v>0.1636525473463492</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3582550571215402</v>
+        <v>0.2764684134380611</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2883133390524981</v>
+        <v>0.2755437122226828</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3794846528828273</v>
+        <v>0.3209484502728046</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2011827706718122</v>
+        <v>0.3960317862988075</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4067982093875415</v>
+        <v>0.238071622933847</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3000320034044356</v>
+        <v>0.2558736746463922</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2580580739111048</v>
+        <v>0.2480818260712528</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2837963236597884</v>
+        <v>0.1582493013176834</v>
       </c>
       <c r="N4" t="n">
-        <v>0.372864948760065</v>
+        <v>0.2934702171273582</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2763866024369102</v>
+        <v>0.2497009792486758</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2764822467040478</v>
+        <v>0.2915951290157297</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3304384438794377</v>
+        <v>0.3035757910474505</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2800025643719463</v>
+        <v>0.3512319648029359</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2679913023195051</v>
+        <v>0.2813873346881437</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4023475479373442</v>
+        <v>0.4761053428246647</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4565864293109401</v>
+        <v>0.3682529668144919</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5514113724785469</v>
+        <v>0.3339213432661763</v>
       </c>
       <c r="W4" t="n">
-        <v>0.407956003963576</v>
+        <v>0.2337068584697402</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3238203065733249</v>
+        <v>0.1732331996857273</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4004051780851396</v>
+        <v>0.3496938644575716</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4109342969463929</v>
+        <v>0.3808059118820377</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3383231471024534</v>
+        <v>0.1877462790026971</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3441175683383909</v>
+        <v>0.2366461367886144</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2462335822360572</v>
+        <v>0.2139888543473405</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4438717894013525</v>
+        <v>0.270120746795449</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4233632999191592</v>
+        <v>0.2299701983830411</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3209167797192633</v>
+        <v>0.1707344096158784</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3929247145358267</v>
+        <v>0.424540880590208</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.2565369289025155</v>
+        <v>0.2878125083453043</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.3177593489337315</v>
+        <v>0.1386477974872029</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.2553521665087906</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.2864574008643716</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.8325546111576978</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.4820203983786536</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.4692898071968737</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.4046124920473814</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.3437758518575662</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.3253913436534809</v>
+        <v>0.135841523652509</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1666474632714857</v>
+        <v>0.2819885678330677</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2913034928944097</v>
+        <v>0.3099645092875766</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2575033781905981</v>
+        <v>0.1636525473463492</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2065978378249685</v>
+        <v>0.2489985863296655</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2870690518320825</v>
+        <v>0.3358195586464345</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4490265477554874</v>
+        <v>0.2851182794313141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3055732406562424</v>
+        <v>0.398849671883664</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3158938037234925</v>
+        <v>0.2217932030931102</v>
       </c>
       <c r="K5" t="n">
-        <v>0.334147023816715</v>
+        <v>0.1475690094928128</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3852140388252823</v>
+        <v>0.2265879795283068</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1841954084497212</v>
+        <v>0.2490616780185371</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2499119900922806</v>
+        <v>0.2326188597850967</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1905301926385229</v>
+        <v>0.266332185526805</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1377782410072799</v>
+        <v>0.2719573997512788</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.224819493166041</v>
+        <v>0.2442838782307004</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2928167531206076</v>
+        <v>0.282353307411843</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3387821966342067</v>
+        <v>0.2329687506522086</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3112511214290918</v>
+        <v>0.4831344284060155</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3261089921377995</v>
+        <v>0.2500701750191489</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6762710228795454</v>
+        <v>0.2961054850300533</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3398085777143913</v>
+        <v>0.122196142405585</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3134962689759163</v>
+        <v>0.1810189526459118</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5457971026999097</v>
+        <v>0.2364328833614385</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.385802339735325</v>
+        <v>0.2961584188674887</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.3642972418560868</v>
+        <v>0.1977752315198593</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2620492424092982</v>
+        <v>0.1504047877106653</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1547323935242761</v>
+        <v>0.2445039186425954</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3124573061015185</v>
+        <v>0.2089277061201505</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3332031301469809</v>
+        <v>0.1765609488011675</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1640426538923894</v>
+        <v>0.2654839942164366</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2545807807437642</v>
+        <v>0.3132287375169506</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.26933875815011</v>
+        <v>0.1977769808344637</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1744319253517568</v>
+        <v>0.1965699711241716</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2347955839344378</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.1371479720446589</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0.7777991260419098</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.4985584931250037</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.3171315793244604</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.3930004818450624</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0.1472318949544184</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.1713994724079775</v>
+        <v>0.1058450470449592</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2965189453783977</v>
+        <v>0.357957190830154</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2596380329829508</v>
+        <v>0.2754829345478712</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3582550571215402</v>
+        <v>0.2764684134380611</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2065978378249685</v>
+        <v>0.2489985863296655</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2474653092750489</v>
+        <v>0.2881974386531615</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4459571813207742</v>
+        <v>0.1266830808441603</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3821761639744235</v>
+        <v>0.3287757035022815</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3206318349043105</v>
+        <v>0.1454715483582812</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2900159797291479</v>
+        <v>0.25166112815634</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4460861907135819</v>
+        <v>0.1997704975487911</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2380154781034752</v>
+        <v>0.2908418718590106</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1381722740903456</v>
+        <v>0.3289125651390187</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1671364296365137</v>
+        <v>0.2731438029429395</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2255160570869348</v>
+        <v>0.1573718655867259</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1373992296862507</v>
+        <v>0.310335328411614</v>
       </c>
       <c r="R6" t="n">
-        <v>0.28423970293113</v>
+        <v>0.2408825277666606</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3614942496960873</v>
+        <v>0.192149190719211</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2348750383614071</v>
+        <v>0.4017859987320677</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3068257123986846</v>
+        <v>0.2189332124096834</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6635265493423909</v>
+        <v>0.177408311670978</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2799832289308404</v>
+        <v>0.2213156257243716</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2390500005087214</v>
+        <v>0.1803578234441186</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5409638925321981</v>
+        <v>0.3203476338375398</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2659356477129398</v>
+        <v>0.35069858793076</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2986432942397962</v>
+        <v>0.2548520923431914</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1977101063296139</v>
+        <v>0.2155285551068835</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2270511528876104</v>
+        <v>0.2804309971073917</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.181730913428489</v>
+        <v>0.3015554053040126</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2315866362877967</v>
+        <v>0.1654004490593198</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2045440901289942</v>
+        <v>0.3839217956449147</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1968388127013928</v>
+        <v>0.312666672915825</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2940922097177937</v>
+        <v>0.1915242751212803</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.14495595835128</v>
+        <v>0.3307230944399311</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2315229413152039</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.26371747713521</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0.6841661877711658</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.3854593817615485</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.2189481565163989</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.2806333352377638</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0.2286624029848918</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.1375405977880776</v>
+        <v>0.3006342508942455</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3636747830766739</v>
+        <v>0.3289563846085855</v>
       </c>
       <c r="C7" t="n">
-        <v>0.252321103760753</v>
+        <v>0.1947039802039447</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2883133390524981</v>
+        <v>0.2755437122226828</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2870690518320825</v>
+        <v>0.3358195586464345</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2474653092750489</v>
+        <v>0.2881974386531615</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4019426939212098</v>
+        <v>0.2767847665111195</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2397417528733443</v>
+        <v>0.1942657745720429</v>
       </c>
       <c r="J7" t="n">
-        <v>0.345943098380229</v>
+        <v>0.2662603159170903</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1128854660925635</v>
+        <v>0.3958860714636813</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2750173312319213</v>
+        <v>0.2807324359881797</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2064147585587781</v>
+        <v>0.2904512339765307</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2655577380870517</v>
+        <v>0.4247904447868093</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1542438429665406</v>
+        <v>0.2993803310038564</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2785704636754484</v>
+        <v>0.2457844505324574</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2752216920837275</v>
+        <v>0.4034780874811045</v>
       </c>
       <c r="R7" t="n">
-        <v>0.228561753157009</v>
+        <v>0.3836890421655063</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2081082052410967</v>
+        <v>0.3243464880213876</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3250599781402083</v>
+        <v>0.4372895595740331</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3489914946154316</v>
+        <v>0.415144050521136</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4868541952890771</v>
+        <v>0.3166843214295752</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2097726476071844</v>
+        <v>0.3597399124471782</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1827811055696121</v>
+        <v>0.2722121453066292</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3994791356457655</v>
+        <v>0.4782234824431362</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1771629897004359</v>
+        <v>0.4516554903399846</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.157915469238131</v>
+        <v>0.3095085408705507</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2531197814030105</v>
+        <v>0.3907446173664889</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2428667572188161</v>
+        <v>0.3426959890762116</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3368240115597659</v>
+        <v>0.3657995330222239</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2823384133712276</v>
+        <v>0.2900617150881523</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2696569355149389</v>
+        <v>0.3120253084986568</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.2744717879729855</v>
+        <v>0.5051795036298905</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.3229621662024001</v>
+        <v>0.3469741861582016</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2757389955224818</v>
+        <v>0.3421131223762436</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1393552452425942</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.3725966430942491</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.7694155380506558</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.3384774576731563</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.4010132861305519</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.2297636297043361</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.3353345301061202</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.2854464972108733</v>
+        <v>0.345609306582935</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.438287842693098</v>
+        <v>0.3918216004813274</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4894442588983932</v>
+        <v>0.2946439565084543</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3794846528828273</v>
+        <v>0.3209484502728046</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4490265477554874</v>
+        <v>0.2851182794313141</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4459571813207742</v>
+        <v>0.1266830808441603</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4019426939212098</v>
+        <v>0.2767847665111195</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.47942179560038</v>
+        <v>0.2652096994049623</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5884120180887917</v>
+        <v>0.1800352803991608</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4152951300066946</v>
+        <v>0.2999449396867758</v>
       </c>
       <c r="L8" t="n">
-        <v>0.474237083862389</v>
+        <v>0.2041542563567942</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4255313506402532</v>
+        <v>0.3563542088779875</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4708296380801647</v>
+        <v>0.3801931629849677</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4515675329190467</v>
+        <v>0.2650448751067294</v>
       </c>
       <c r="P8" t="n">
-        <v>0.452760046196219</v>
+        <v>0.1274484462890025</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4138545144604237</v>
+        <v>0.3017777900951241</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2907260159613025</v>
+        <v>0.2409246598953911</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4553247102262254</v>
+        <v>0.200659766586863</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3561502367677504</v>
+        <v>0.3643945842929213</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6013975699646552</v>
+        <v>0.2084347530793544</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5770167811612308</v>
+        <v>0.1354636190646089</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4380646054423837</v>
+        <v>0.2512229964000722</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4162659696665874</v>
+        <v>0.2177534255267048</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3312914291137389</v>
+        <v>0.3325222714115795</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.4364103978262921</v>
+        <v>0.3358463403150813</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.3772695121329084</v>
+        <v>0.3175824090963201</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4346214844121113</v>
+        <v>0.2756137849419807</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.4374551282382673</v>
+        <v>0.3095924912919123</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.4877275043974274</v>
+        <v>0.3543358226048736</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.4500773365293429</v>
+        <v>0.2107960197503087</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.4284740431420084</v>
+        <v>0.402490866130974</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.454403546636226</v>
+        <v>0.3237489535876773</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.4316282625884242</v>
+        <v>0.2357530514192114</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.4405301473187531</v>
+        <v>0.3927348255203867</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.4408610644882873</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.4938900342880537</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.5214502029138955</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.5395348268068524</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.4754268669166877</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.5043557289649575</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.4257066487753154</v>
+        <v>0.3308297030454014</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3545868537848112</v>
+        <v>0.4463351066470099</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3250731689920256</v>
+        <v>0.304493895682044</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2011827706718122</v>
+        <v>0.3960317862988075</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3055732406562424</v>
+        <v>0.398849671883664</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3821761639744235</v>
+        <v>0.3287757035022815</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2397417528733443</v>
+        <v>0.1942657745720429</v>
       </c>
       <c r="H9" t="n">
-        <v>0.47942179560038</v>
+        <v>0.2652096994049623</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3643032105280071</v>
+        <v>0.3336661304621701</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2548698168488124</v>
+        <v>0.453059402471725</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1447946769337945</v>
+        <v>0.3527139295256727</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2663396173310491</v>
+        <v>0.4161392232450403</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3842365153297232</v>
+        <v>0.4829238458488726</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2531646002810881</v>
+        <v>0.3340941211847055</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3025256099317074</v>
+        <v>0.2499646332789821</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3846397399564536</v>
+        <v>0.4219402091075986</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3398865464505034</v>
+        <v>0.3794271413604903</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1983564317231474</v>
+        <v>0.3655595654062899</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4614443691103732</v>
+        <v>0.3800930776280604</v>
       </c>
       <c r="U9" t="n">
-        <v>0.380482570952737</v>
+        <v>0.390590952906771</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4842040032477962</v>
+        <v>0.2998171297805196</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3597876097637442</v>
+        <v>0.4049227291181428</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3084860429840908</v>
+        <v>0.3631355722007285</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4431268165185223</v>
+        <v>0.5109749094858135</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3718358242984632</v>
+        <v>0.4452759598873044</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3162142876268748</v>
+        <v>0.4158070103921356</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3587184311389142</v>
+        <v>0.4438046579377176</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2736182420158469</v>
+        <v>0.4287793197201197</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.4607590640620282</v>
+        <v>0.4271854950494071</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.4281318005672624</v>
+        <v>0.3396466661682929</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.3321445358818296</v>
+        <v>0.4372812722741581</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.3831847160328181</v>
+        <v>0.5024441308808834</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.3349507309513756</v>
+        <v>0.380311714929703</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.3561236736898169</v>
+        <v>0.4596402033607281</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.2191586470705325</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.3662758907675144</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.4525730861764261</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.4982125687883669</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.3721323822820192</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.3602270195424285</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.3759923499814662</v>
+        <v>0.4295336931374962</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DRC</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3352985487834386</v>
+        <v>0.3446252878661659</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3661683188435101</v>
+        <v>0.2723004253443609</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4067982093875415</v>
+        <v>0.238071622933847</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3158938037234925</v>
+        <v>0.2217932030931102</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3206318349043105</v>
+        <v>0.1454715483582812</v>
       </c>
       <c r="G10" t="n">
-        <v>0.345943098380229</v>
+        <v>0.2662603159170903</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5884120180887917</v>
+        <v>0.1800352803991608</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3643032105280071</v>
+        <v>0.3336661304621701</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.340650303333233</v>
+        <v>0.2572225439009428</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3718026824077654</v>
+        <v>0.1764632632623092</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2616640702234723</v>
+        <v>0.2954106407034373</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2452391442867736</v>
+        <v>0.3670785627921129</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2693425792742609</v>
+        <v>0.2945901225766548</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3772746800857064</v>
+        <v>0.1793581875466885</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2992885760917779</v>
+        <v>0.3117072827926232</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4455863148633519</v>
+        <v>0.2570558197502032</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3180309358887342</v>
+        <v>0.2171760303637006</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4023782277311932</v>
+        <v>0.4462602517295349</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3204801993158633</v>
+        <v>0.2570998209363994</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5800105747405501</v>
+        <v>0.2623848739343279</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3729856385194187</v>
+        <v>0.2252530417732165</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3808606536817538</v>
+        <v>0.1686632824406984</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5932065221301239</v>
+        <v>0.3124822916822513</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.3469846996856064</v>
+        <v>0.3589383577746276</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.4133035840967512</v>
+        <v>0.2427520961586564</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2413065612270026</v>
+        <v>0.2386590613897018</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2400440558748673</v>
+        <v>0.246818431803476</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.284973432918567</v>
+        <v>0.2754525613902492</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.327840193564598</v>
+        <v>0.1396563613514463</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3786385332900696</v>
+        <v>0.3232800799654633</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.2947456163018362</v>
+        <v>0.3466441231576973</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.3553873301078261</v>
+        <v>0.2127553642329386</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.289665966575825</v>
+        <v>0.2868600540121342</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.2718911139006169</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.3394653398630165</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0.6830843423018097</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.4015255323802023</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.4031437948588085</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.3414339010040642</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.3555585207807144</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.3310995879994968</v>
+        <v>0.2777730236961127</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.375576582308957</v>
+        <v>0.3220565418753426</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2640095521711325</v>
+        <v>0.3638787036627291</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3000320034044356</v>
+        <v>0.2558736746463922</v>
       </c>
       <c r="E11" t="n">
-        <v>0.334147023816715</v>
+        <v>0.1475690094928128</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2900159797291479</v>
+        <v>0.25166112815634</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1128854660925635</v>
+        <v>0.3958860714636813</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4152951300066946</v>
+        <v>0.2999449396867758</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2548698168488124</v>
+        <v>0.453059402471725</v>
       </c>
       <c r="J11" t="n">
-        <v>0.340650303333233</v>
+        <v>0.2572225439009428</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2497207091241017</v>
+        <v>0.2459776129581644</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2557077618692024</v>
+        <v>0.300972375638532</v>
       </c>
       <c r="N11" t="n">
-        <v>0.273138959299096</v>
+        <v>0.1727132836323507</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1887392748129846</v>
+        <v>0.3296286531108251</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3207582427214263</v>
+        <v>0.2906746802309619</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2768250609081356</v>
+        <v>0.2770857428410363</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2382564909778369</v>
+        <v>0.3202039280359151</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1475279052397341</v>
+        <v>0.2203476837133999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3282103356579352</v>
+        <v>0.507503032379004</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3637670673775442</v>
+        <v>0.2164261223567816</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4486442029035177</v>
+        <v>0.305914560282199</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2338798764374103</v>
+        <v>0.07104678919648819</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1548105853834086</v>
+        <v>0.1880854962122692</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3873269193617946</v>
+        <v>0.2034263921640788</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1635080678383613</v>
+        <v>0.3453141743960039</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1202321507430047</v>
+        <v>0.2260787600462652</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.23490564641881</v>
+        <v>0.1144677980255647</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2585646523704642</v>
+        <v>0.250239835696435</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.3367874327373435</v>
+        <v>0.1990854782380168</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.2903615193835818</v>
+        <v>0.1893572594252143</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.3249573634445214</v>
+        <v>0.3418422981571004</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.3019984364084913</v>
+        <v>0.2243420539475923</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.2953882293207462</v>
+        <v>0.1543913568233148</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.2870980172465573</v>
+        <v>0.2547189410401388</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1557920284559451</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.3918690267233366</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0.7339719654015158</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.2648015290392599</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.4281371796033307</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.2013379584309059</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.3694877950117928</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.3216629530074162</v>
+        <v>0.1783481463172394</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3963325722961649</v>
+        <v>0.3422107334198201</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3878952776785592</v>
+        <v>0.3191261707614903</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2580580739111048</v>
+        <v>0.2480818260712528</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3852140388252823</v>
+        <v>0.2265879795283068</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4460861907135819</v>
+        <v>0.1997704975487911</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2750173312319213</v>
+        <v>0.2807324359881797</v>
       </c>
       <c r="H12" t="n">
-        <v>0.474237083862389</v>
+        <v>0.2041542563567942</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1447946769337945</v>
+        <v>0.3527139295256727</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3718026824077654</v>
+        <v>0.1764632632623092</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2497207091241017</v>
+        <v>0.2459776129581644</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2973024747609714</v>
+        <v>0.2894829879333319</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4150038431149247</v>
+        <v>0.3317420212591861</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3202362928661445</v>
+        <v>0.2436714819259217</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3992012734033009</v>
+        <v>0.2524032932300396</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4213519450701368</v>
+        <v>0.2293146508506982</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3689781714911573</v>
+        <v>0.2352428263006031</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1581863799597457</v>
+        <v>0.1561532993768578</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4748576458496833</v>
+        <v>0.503256932790087</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4459365646358276</v>
+        <v>0.2715403446259205</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3922496984426169</v>
+        <v>0.2369442115691905</v>
       </c>
       <c r="W12" t="n">
-        <v>0.381743037331562</v>
+        <v>0.2254975989086316</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3479489328168894</v>
+        <v>0.1917531674768638</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4000375895494668</v>
+        <v>0.2871812531163396</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.3676392803492771</v>
+        <v>0.3013003848172541</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.3211549153524123</v>
+        <v>0.2270727433005399</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3675051492093114</v>
+        <v>0.2482888307606567</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3101361068043093</v>
+        <v>0.2936329084251146</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.4802720233502358</v>
+        <v>0.311908412843902</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.4333881691294119</v>
+        <v>0.2265040841907006</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.4157136601373941</v>
+        <v>0.3147907625132514</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.4149813512023821</v>
+        <v>0.3630878678236224</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.3711795891662545</v>
+        <v>0.2419380223010046</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.408770764524723</v>
+        <v>0.3018349840698071</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.264467304943567</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0.4370029314465217</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.4260807810402555</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.56203626390631</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.3840038626906518</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.4452210869874537</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.4362331980695221</v>
+        <v>0.2554258500563629</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2611821056023608</v>
+        <v>0.2551825683450369</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2974565459129302</v>
+        <v>0.2583035212512218</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2837963236597884</v>
+        <v>0.1582493013176834</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1841954084497212</v>
+        <v>0.2490616780185371</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2380154781034752</v>
+        <v>0.2908418718590106</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2064147585587781</v>
+        <v>0.2904512339765307</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4255313506402532</v>
+        <v>0.3563542088779875</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2663396173310491</v>
+        <v>0.4161392232450403</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2616640702234723</v>
+        <v>0.2954106407034373</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2557077618692024</v>
+        <v>0.300972375638532</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2973024747609714</v>
+        <v>0.2894829879333319</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2340894883016717</v>
+        <v>0.2752104884305469</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1793437717989436</v>
+        <v>0.2536612280391606</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2596093461627262</v>
+        <v>0.3392496676483632</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2503816571717621</v>
+        <v>0.3361475258370989</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2907784684134964</v>
+        <v>0.3678632134611118</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2615621648857203</v>
+        <v>0.2767347773585403</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2962039894877369</v>
+        <v>0.4933448176698354</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3489402249921671</v>
+        <v>0.4053250063125022</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5659248620702423</v>
+        <v>0.3489706366726611</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2703364956248626</v>
+        <v>0.2956027901282651</v>
       </c>
       <c r="X13" t="n">
-        <v>0.30067128251811</v>
+        <v>0.2449941495020842</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4732715740554824</v>
+        <v>0.4245820726160768</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2931169136921485</v>
+        <v>0.4422793241262977</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.3073424219506963</v>
+        <v>0.1311562763729155</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.2236488566201493</v>
+        <v>0.271934170363202</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1516761134086641</v>
+        <v>0.3058007698738928</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2927582696240481</v>
+        <v>0.2620596493976464</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.257017643359763</v>
+        <v>0.2886134161636775</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2464355140252383</v>
+        <v>0.2851140986416889</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.2333511689069191</v>
+        <v>0.4692312641972033</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3277760889909939</v>
+        <v>0.329432727257408</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.2383959462137812</v>
+        <v>0.1577740962322733</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.1904783415195095</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.2857520503096467</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0.7855226121195802</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.4398060125844658</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.3927497614230813</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.340641455368389</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.2810172913006456</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.243600129768574</v>
+        <v>0.2397702027888547</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2833457778512003</v>
+        <v>0.3369423203761147</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3027753782939155</v>
+        <v>0.3908331283267535</v>
       </c>
       <c r="D14" t="n">
-        <v>0.372864948760065</v>
+        <v>0.2934702171273582</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2499119900922806</v>
+        <v>0.2326188597850967</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1381722740903456</v>
+        <v>0.3289125651390187</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2655577380870517</v>
+        <v>0.4247904447868093</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4708296380801647</v>
+        <v>0.3801931629849677</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3842365153297232</v>
+        <v>0.4829238458488726</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2452391442867736</v>
+        <v>0.3670785627921129</v>
       </c>
       <c r="K14" t="n">
-        <v>0.273138959299096</v>
+        <v>0.1727132836323507</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4150038431149247</v>
+        <v>0.3317420212591861</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2340894883016717</v>
+        <v>0.2752104884305469</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.196654787623802</v>
+        <v>0.3414896798475637</v>
       </c>
       <c r="P14" t="n">
-        <v>0.297683963037188</v>
+        <v>0.3676518698323921</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1274392190205437</v>
+        <v>0.3216594976536126</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3226980088217037</v>
+        <v>0.3911144565432526</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3199910628392785</v>
+        <v>0.2732399508985547</v>
       </c>
       <c r="T14" t="n">
-        <v>0.247585451173478</v>
+        <v>0.5156188902704043</v>
       </c>
       <c r="U14" t="n">
-        <v>0.324232384868832</v>
+        <v>0.3109850864383918</v>
       </c>
       <c r="V14" t="n">
-        <v>0.622542614322984</v>
+        <v>0.3400356509520611</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3038665670709292</v>
+        <v>0.2000460838827972</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2656790673127889</v>
+        <v>0.2765064455359365</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5465009326320198</v>
+        <v>0.3188256286398068</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.244933003448704</v>
+        <v>0.3999566664363042</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3030575264577114</v>
+        <v>0.2369121076069145</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.1151007954285409</v>
+        <v>0.2031001409225986</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1886686464263574</v>
+        <v>0.3308980689049165</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.1062657869119027</v>
+        <v>0.2231507160273779</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.1993915889238514</v>
+        <v>0.2944524973464878</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.272346704366664</v>
+        <v>0.3858148657342722</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.1597987648806432</v>
+        <v>0.3200356248880099</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.2706653342670165</v>
+        <v>0.2607160018338174</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.1469154529729303</v>
+        <v>0.2660382563401724</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.2156668989353693</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.2944623851594366</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0.6625376626544052</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.3210300798750583</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0.2349961211140964</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.2503882224809887</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0.2810390671408994</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.1589464533120713</v>
+        <v>0.2262663055798564</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2849203707821831</v>
+        <v>0.3413139521876343</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2003139282020396</v>
+        <v>0.2930797335697531</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2763866024369102</v>
+        <v>0.2497009792486758</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1905301926385229</v>
+        <v>0.266332185526805</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1671364296365137</v>
+        <v>0.2731438029429395</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1542438429665406</v>
+        <v>0.2993803310038564</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4515675329190467</v>
+        <v>0.2650448751067294</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2531646002810881</v>
+        <v>0.3340941211847055</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2693425792742609</v>
+        <v>0.2945901225766548</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1887392748129846</v>
+        <v>0.3296286531108251</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3202362928661445</v>
+        <v>0.2436714819259217</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1793437717989436</v>
+        <v>0.2536612280391606</v>
       </c>
       <c r="N15" t="n">
-        <v>0.196654787623802</v>
+        <v>0.3414896798475637</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1891752806071109</v>
+        <v>0.3088000098495299</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1865619538300724</v>
+        <v>0.1821605032944059</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2608570941091103</v>
+        <v>0.2437067541293812</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2353399219945959</v>
+        <v>0.2117953463024462</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3028577497573935</v>
+        <v>0.4091307891276067</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2686359889081562</v>
+        <v>0.3248304771512204</v>
       </c>
       <c r="V15" t="n">
-        <v>0.574973561385391</v>
+        <v>0.2136992180319786</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2413733660214175</v>
+        <v>0.2921295830790761</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1844279358613195</v>
+        <v>0.2792393694156582</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4828205814514998</v>
+        <v>0.3795498872837161</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.2350619597351292</v>
+        <v>0.3190946878008364</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.2424764878796981</v>
+        <v>0.2605796191359893</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.1872440773633686</v>
+        <v>0.2755389364395295</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1690594872972605</v>
+        <v>0.3439665193207485</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.2710524352564069</v>
+        <v>0.3657031785604838</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.2783962922543017</v>
+        <v>0.3199132722385548</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2044983041306346</v>
+        <v>0.3469502433990936</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2370359622758108</v>
+        <v>0.4338261063383205</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.2581445800081346</v>
+        <v>0.3501974904777392</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.1683926080566518</v>
+        <v>0.3207444093340364</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1083870105543655</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0.2609657311555733</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0.7206586284775655</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.3601240817628735</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0.3304434899278499</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.2368961961518657</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.2275848286563561</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0.2151318758603338</v>
+        <v>0.2760331636701563</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2611925164018816</v>
+        <v>0.3379547227235137</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2085398669304941</v>
+        <v>0.237238249223889</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2764822467040478</v>
+        <v>0.2915951290157297</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1377782410072799</v>
+        <v>0.2719573997512788</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2255160570869348</v>
+        <v>0.1573718655867259</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2785704636754484</v>
+        <v>0.2457844505324574</v>
       </c>
       <c r="H16" t="n">
-        <v>0.452760046196219</v>
+        <v>0.1274484462890025</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3025256099317074</v>
+        <v>0.2499646332789821</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3772746800857064</v>
+        <v>0.1793581875466885</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3207582427214263</v>
+        <v>0.2906746802309619</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3992012734033009</v>
+        <v>0.2524032932300396</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2596093461627262</v>
+        <v>0.3392496676483632</v>
       </c>
       <c r="N16" t="n">
-        <v>0.297683963037188</v>
+        <v>0.3676518698323921</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1891752806071109</v>
+        <v>0.3088000098495299</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2586298549606002</v>
+        <v>0.3632341287834439</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2540448600746285</v>
+        <v>0.3233194531170124</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3464667158589136</v>
+        <v>0.2597044299689192</v>
       </c>
       <c r="T16" t="n">
-        <v>0.329499267561866</v>
+        <v>0.3473929856459481</v>
       </c>
       <c r="U16" t="n">
-        <v>0.274384483651289</v>
+        <v>0.2567860831693242</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6869344888858391</v>
+        <v>0.2173730471979161</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3035263238067648</v>
+        <v>0.2389614271571897</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2577521899608216</v>
+        <v>0.1768418593365303</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5553347324974152</v>
+        <v>0.3651801723336197</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.3850821600559948</v>
+        <v>0.3963523643399152</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.3267058910351817</v>
+        <v>0.3164432950214119</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.3041155606027348</v>
+        <v>0.2850450047992735</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2368239230019384</v>
+        <v>0.2560714758662188</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.3573501051044435</v>
+        <v>0.3166767993235384</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.373997417730279</v>
+        <v>0.1513124620332173</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1171677869939665</v>
+        <v>0.3613739903776846</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.2871337624947748</v>
+        <v>0.3358993760640132</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.2756172666041503</v>
+        <v>0.2025723347783263</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.1974899975122066</v>
+        <v>0.3599671172658837</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.2479409044525452</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0.1887781816972272</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0.7658615029982968</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.4890704623309902</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0.321057201007127</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.3823178671118937</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0.1075492301261601</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0.216089682725531</v>
+        <v>0.306761728632114</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2438531203230072</v>
+        <v>0.4022916873690882</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2912905338157356</v>
+        <v>0.4027614882947793</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3304384438794377</v>
+        <v>0.3035757910474505</v>
       </c>
       <c r="E17" t="n">
-        <v>0.224819493166041</v>
+        <v>0.2442838782307004</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1373992296862507</v>
+        <v>0.310335328411614</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2752216920837275</v>
+        <v>0.4034780874811045</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4138545144604237</v>
+        <v>0.3017777900951241</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3846397399564536</v>
+        <v>0.4219402091075986</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2992885760917779</v>
+        <v>0.3117072827926232</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2768250609081356</v>
+        <v>0.2770857428410363</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4213519450701368</v>
+        <v>0.2293146508506982</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2503816571717621</v>
+        <v>0.3361475258370989</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1274392190205437</v>
+        <v>0.3216594976536126</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1865619538300724</v>
+        <v>0.1821605032944059</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2586298549606002</v>
+        <v>0.3632341287834439</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2808656260331973</v>
+        <v>0.2170905611164123</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3206248712277627</v>
+        <v>0.1895240777861922</v>
       </c>
       <c r="T17" t="n">
-        <v>0.223266051072815</v>
+        <v>0.4879434962063667</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3439725169484816</v>
+        <v>0.267688540398931</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6363991497077688</v>
+        <v>0.2611318256406168</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3190841473881219</v>
+        <v>0.2549074504555367</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2415937040744993</v>
+        <v>0.3078938447096166</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5131993728420714</v>
+        <v>0.270461537863202</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.2682172587295527</v>
+        <v>0.2407168142818222</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.2999912038583119</v>
+        <v>0.2865440452204629</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.110819558083858</v>
+        <v>0.2336628585536174</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1859745577497603</v>
+        <v>0.3600896475511293</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.1569041688143598</v>
+        <v>0.3539858620774821</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.2546827134241861</v>
+        <v>0.3315889110613328</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.2464303393933069</v>
+        <v>0.3852659046310177</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.212716647756272</v>
+        <v>0.3608730394837131</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.2150443012987401</v>
+        <v>0.337487170711645</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.09443094600793056</v>
+        <v>0.3425174267975587</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2182604499535152</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0.2505674264817183</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0.6596625842296384</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.3451287608700729</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0.262994007298524</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.2557558953387334</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0.256449520662638</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0.1538581827981373</v>
+        <v>0.2696358584746515</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3350891621522544</v>
+        <v>0.4702634547527632</v>
       </c>
       <c r="C18" t="n">
-        <v>0.268584286460668</v>
+        <v>0.4192985205160406</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2800025643719463</v>
+        <v>0.3512319648029359</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2928167531206076</v>
+        <v>0.282353307411843</v>
       </c>
       <c r="F18" t="n">
-        <v>0.28423970293113</v>
+        <v>0.2408825277666606</v>
       </c>
       <c r="G18" t="n">
-        <v>0.228561753157009</v>
+        <v>0.3836890421655063</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2907260159613025</v>
+        <v>0.2409246598953911</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3398865464505034</v>
+        <v>0.3794271413604903</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4455863148633519</v>
+        <v>0.2570558197502032</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2382564909778369</v>
+        <v>0.3202039280359151</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3689781714911573</v>
+        <v>0.2352428263006031</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2907784684134964</v>
+        <v>0.3678632134611118</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3226980088217037</v>
+        <v>0.3911144565432526</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2608570941091103</v>
+        <v>0.2437067541293812</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2540448600746285</v>
+        <v>0.3233194531170124</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2808656260331973</v>
+        <v>0.2170905611164123</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3126878596201679</v>
+        <v>0.217552798162153</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2281573359172408</v>
+        <v>0.4983415318438928</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4109675800646358</v>
+        <v>0.2228159047789484</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5879080239213959</v>
+        <v>0.2263354517372629</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2329231438315876</v>
+        <v>0.2979466553743868</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1956796999812876</v>
+        <v>0.3323372001661206</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.4047166276668345</v>
+        <v>0.3140776100745333</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.3064434835588242</v>
+        <v>0.2412572264096745</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.1824876844721048</v>
+        <v>0.3070411406148059</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.3052126415154512</v>
+        <v>0.2801567595235592</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.2987065171370876</v>
+        <v>0.4140185202139181</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.3697362932547953</v>
+        <v>0.3689316399724785</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.3122924100575596</v>
+        <v>0.3072406552176908</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.2629511725859354</v>
+        <v>0.4467056309920243</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.3211812495919816</v>
+        <v>0.3708334269410775</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.3000943395384623</v>
+        <v>0.3083302830246252</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.2833912761296503</v>
+        <v>0.3932125257282984</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2788974450055725</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0.3364848871532977</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0.7706425957871538</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0.4053461000607541</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0.4020600942911589</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0.3489478498041539</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0.320685064849072</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0.2881792163590601</v>
+        <v>0.3523096826171525</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3461741770942514</v>
+        <v>0.3778380270460248</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3190999396781072</v>
+        <v>0.3438310488166891</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2679913023195051</v>
+        <v>0.2813873346881437</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3387821966342067</v>
+        <v>0.2329687506522086</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3614942496960873</v>
+        <v>0.192149190719211</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2081082052410967</v>
+        <v>0.3243464880213876</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4553247102262254</v>
+        <v>0.200659766586863</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1983564317231474</v>
+        <v>0.3655595654062899</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3180309358887342</v>
+        <v>0.2171760303637006</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1475279052397341</v>
+        <v>0.2203476837133999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1581863799597457</v>
+        <v>0.1561532993768578</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2615621648857203</v>
+        <v>0.2767347773585403</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3199910628392785</v>
+        <v>0.2732399508985547</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2353399219945959</v>
+        <v>0.2117953463024462</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3464667158589136</v>
+        <v>0.2597044299689192</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3206248712277627</v>
+        <v>0.1895240777861922</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3126878596201679</v>
+        <v>0.217552798162153</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4033634788843908</v>
+        <v>0.4507345980717968</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3851644179278813</v>
+        <v>0.2103456867061862</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4215110479186239</v>
+        <v>0.1963278666021328</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3291633399436159</v>
+        <v>0.1984451862339849</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2506777150115004</v>
+        <v>0.216760436439679</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4114742838577523</v>
+        <v>0.282838223275526</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.2751493417912679</v>
+        <v>0.3204378079517</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.2391853678590214</v>
+        <v>0.1989890170841504</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.261485730875094</v>
+        <v>0.1920489559368984</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.2365923136771954</v>
+        <v>0.3099324041488422</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.3880062832819917</v>
+        <v>0.2725155389985139</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.3651425952731092</v>
+        <v>0.2403229887216632</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.3607241389361425</v>
+        <v>0.3848524562881842</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.3411455949910237</v>
+        <v>0.3149377175302987</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.2718714238986559</v>
+        <v>0.2463875544711105</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.3155749260440156</v>
+        <v>0.3130694637664324</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1663039272707412</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0.3889987239186525</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0.7695198560805719</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.321125352750404</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0.4803650487846528</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0.2723577801231682</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0.3870290496972799</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.3574078085119932</v>
+        <v>0.2717710195933907</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3402511101860129</v>
+        <v>0.4820229033299572</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3269628209310923</v>
+        <v>0.3696217902733633</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4023475479373442</v>
+        <v>0.4761053428246647</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3112511214290918</v>
+        <v>0.4831344284060155</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2348750383614071</v>
+        <v>0.4017859987320677</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3250599781402083</v>
+        <v>0.4372895595740331</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3561502367677504</v>
+        <v>0.3643945842929213</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4614443691103732</v>
+        <v>0.3800930776280604</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4023782277311932</v>
+        <v>0.4462602517295349</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3282103356579352</v>
+        <v>0.507503032379004</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4748576458496833</v>
+        <v>0.503256932790087</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2962039894877369</v>
+        <v>0.4933448176698354</v>
       </c>
       <c r="N20" t="n">
-        <v>0.247585451173478</v>
+        <v>0.5156188902704043</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3028577497573935</v>
+        <v>0.4091307891276067</v>
       </c>
       <c r="P20" t="n">
-        <v>0.329499267561866</v>
+        <v>0.3473929856459481</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.223266051072815</v>
+        <v>0.4879434962063667</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2281573359172408</v>
+        <v>0.4983415318438928</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4033634788843908</v>
+        <v>0.4507345980717968</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4268885043534845</v>
+        <v>0.4388132635802751</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6599391054314288</v>
+        <v>0.3626084512982103</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2712602664909509</v>
+        <v>0.456926820586612</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2829029846773811</v>
+        <v>0.4288386805601746</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.4903354286097076</v>
+        <v>0.5419067788466096</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.3124124749183476</v>
+        <v>0.5389900353968659</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.2948960494433945</v>
+        <v>0.5182368376404581</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.2545333145138796</v>
+        <v>0.456279646593099</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3138389917979056</v>
+        <v>0.4302504296636231</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.2379864999940971</v>
+        <v>0.51933577976279</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.1936700557149172</v>
+        <v>0.4327022459340723</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.3171854728831933</v>
+        <v>0.538842557744599</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.2843246247454799</v>
+        <v>0.4778764466037598</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.354592809618933</v>
+        <v>0.4743543462246376</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.2622437538190898</v>
+        <v>0.5398244413442074</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.3487808285335481</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0.3330052073194309</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0.6765377254040345</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0.3989539263810629</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0.344543231116638</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0.3733814292209105</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0.3397281741180733</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.2688398240265304</v>
+        <v>0.4915108850606058</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4298678384060649</v>
+        <v>0.45224383602069</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1913193787943113</v>
+        <v>0.4152538522828616</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4565864293109401</v>
+        <v>0.3682529668144919</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3261089921377995</v>
+        <v>0.2500701750191489</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3068257123986846</v>
+        <v>0.2189332124096834</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3489914946154316</v>
+        <v>0.415144050521136</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6013975699646552</v>
+        <v>0.2084347530793544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.380482570952737</v>
+        <v>0.390590952906771</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3204801993158633</v>
+        <v>0.2570998209363994</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3637670673775442</v>
+        <v>0.2164261223567816</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4459365646358276</v>
+        <v>0.2715403446259205</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3489402249921671</v>
+        <v>0.4053250063125022</v>
       </c>
       <c r="N21" t="n">
-        <v>0.324232384868832</v>
+        <v>0.3109850864383918</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2686359889081562</v>
+        <v>0.3248304771512204</v>
       </c>
       <c r="P21" t="n">
-        <v>0.274384483651289</v>
+        <v>0.2567860831693242</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3439725169484816</v>
+        <v>0.267688540398931</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4109675800646358</v>
+        <v>0.2228159047789484</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3851644179278813</v>
+        <v>0.2103456867061862</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4268885043534845</v>
+        <v>0.4388132635802751</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6801090539016456</v>
+        <v>0.2174767127957493</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3090318141353591</v>
+        <v>0.1877386911868421</v>
       </c>
       <c r="X21" t="n">
-        <v>0.310374174802984</v>
+        <v>0.2796983507251078</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.6695244960013363</v>
+        <v>0.2340191142161165</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.3750191068880135</v>
+        <v>0.29685964507701</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.3810468844810351</v>
+        <v>0.3286184902442067</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.3353739079332042</v>
+        <v>0.203440816658389</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.3442764590800131</v>
+        <v>0.3512818991942925</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.355597216572326</v>
+        <v>0.3032168782242811</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.4052201491093693</v>
+        <v>0.2341449059515845</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.2671966296816718</v>
+        <v>0.4630810604728939</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.2931429836690956</v>
+        <v>0.1938572196956187</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.3912459109001518</v>
+        <v>0.2059943641364465</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.2874531655190166</v>
+        <v>0.3975474913946244</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.3139496900970591</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0.3635246287155983</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0.6801090539016454</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.447773250086628</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0.3554094072020421</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0.3683676032520843</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0.2466722306350327</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.3334332634662363</v>
+        <v>0.3196542408505018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6679247697882829</v>
+        <v>0.4015146923735201</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6317544851546755</v>
+        <v>0.3206642101259284</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5514113724785469</v>
+        <v>0.3339213432661763</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6762710228795454</v>
+        <v>0.2961054850300533</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6635265493423909</v>
+        <v>0.177408311670978</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4868541952890771</v>
+        <v>0.3166843214295752</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5770167811612308</v>
+        <v>0.1354636190646089</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4842040032477962</v>
+        <v>0.2998171297805196</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5800105747405501</v>
+        <v>0.2623848739343279</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4486442029035177</v>
+        <v>0.305914560282199</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3922496984426169</v>
+        <v>0.2369442115691905</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5659248620702423</v>
+        <v>0.3489706366726611</v>
       </c>
       <c r="N22" t="n">
-        <v>0.622542614322984</v>
+        <v>0.3400356509520611</v>
       </c>
       <c r="O22" t="n">
-        <v>0.574973561385391</v>
+        <v>0.2136992180319786</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6869344888858391</v>
+        <v>0.2173730471979161</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6363991497077688</v>
+        <v>0.2611318256406168</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5879080239213959</v>
+        <v>0.2263354517372629</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4215110479186239</v>
+        <v>0.1963278666021328</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6599391054314288</v>
+        <v>0.3626084512982103</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6801090539016456</v>
+        <v>0.2174767127957493</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5738215509348339</v>
+        <v>0.2641489550167142</v>
       </c>
       <c r="X22" t="n">
-        <v>0.5560603124835647</v>
+        <v>0.2633036921867235</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.3562044888235915</v>
+        <v>0.3351097203461968</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.4790356645298458</v>
+        <v>0.2946738537145007</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.491373584012431</v>
+        <v>0.3230248279726515</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.5768619701795289</v>
+        <v>0.2690591413436109</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.5854347936783967</v>
+        <v>0.3505643942092199</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.6597791385364855</v>
+        <v>0.3807600005363621</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.600631889567089</v>
+        <v>0.2779009940098109</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.6862224498642454</v>
+        <v>0.4247586323691462</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.6408527500479861</v>
+        <v>0.3362986542964774</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.6059704413486603</v>
+        <v>0.2778509324306785</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.6589201771553191</v>
+        <v>0.4051857334215047</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.5148616037469794</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0.7232979270857065</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0.4734574377492569</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0.7612864372785065</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0.4940641360161619</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0.7310069145300502</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0.6782095932856456</v>
+        <v>0.3303726993054028</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.435371867393919</v>
+        <v>0.3033241053052645</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1854963280241858</v>
+        <v>0.3248114595238429</v>
       </c>
       <c r="D23" t="n">
-        <v>0.407956003963576</v>
+        <v>0.2337068584697402</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3398085777143913</v>
+        <v>0.122196142405585</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2799832289308404</v>
+        <v>0.2213156257243716</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2097726476071844</v>
+        <v>0.3597399124471782</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4380646054423837</v>
+        <v>0.2512229964000722</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3597876097637442</v>
+        <v>0.4049227291181428</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3729856385194187</v>
+        <v>0.2252530417732165</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2338798764374103</v>
+        <v>0.07104678919648819</v>
       </c>
       <c r="L23" t="n">
-        <v>0.381743037331562</v>
+        <v>0.2254975989086316</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2703364956248626</v>
+        <v>0.2956027901282651</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3038665670709292</v>
+        <v>0.2000460838827972</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2413733660214175</v>
+        <v>0.2921295830790761</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3035263238067648</v>
+        <v>0.2389614271571897</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.3190841473881219</v>
+        <v>0.2549074504555367</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2329231438315876</v>
+        <v>0.2979466553743868</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3291633399436159</v>
+        <v>0.1984451862339849</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2712602664909509</v>
+        <v>0.456926820586612</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3090318141353591</v>
+        <v>0.1877386911868421</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5738215509348339</v>
+        <v>0.2641489550167142</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2135036587938169</v>
+        <v>0.1522514072717411</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.4900275855011309</v>
+        <v>0.2061076521856845</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.2303151494725369</v>
+        <v>0.3256157915855947</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.2049151572628783</v>
+        <v>0.2303116708808337</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.3004998171987503</v>
+        <v>0.1096737601944663</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.3345660036733711</v>
+        <v>0.2214808775873784</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.3352668188034546</v>
+        <v>0.2105293120693882</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.268491223373315</v>
+        <v>0.1552219888380412</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.2860879798154172</v>
+        <v>0.3229743997733477</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.2857283193787624</v>
+        <v>0.2238325729223176</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.409916400718198</v>
+        <v>0.1415728339178221</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.3131983666267604</v>
+        <v>0.2601207231419383</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.2827334233821683</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0.4037120803673644</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0.7201539425277855</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0.3772939960724236</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0.4105073156227491</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0.3113680858439996</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0.3360798405474507</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0.3383193594118835</v>
+        <v>0.1589490098208889</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3759831064158954</v>
+        <v>0.2189810046139109</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1759476038430624</v>
+        <v>0.2152302121219773</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3238203065733249</v>
+        <v>0.1732331996857273</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3134962689759163</v>
+        <v>0.1810189526459118</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2390500005087214</v>
+        <v>0.1803578234441186</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1827811055696121</v>
+        <v>0.2722121453066292</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4162659696665874</v>
+        <v>0.2177534255267048</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3084860429840908</v>
+        <v>0.3631355722007285</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3808606536817538</v>
+        <v>0.1686632824406984</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1548105853834086</v>
+        <v>0.1880854962122692</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3479489328168894</v>
+        <v>0.1917531674768638</v>
       </c>
       <c r="M24" t="n">
-        <v>0.30067128251811</v>
+        <v>0.2449941495020842</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2656790673127889</v>
+        <v>0.2765064455359365</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1844279358613195</v>
+        <v>0.2792393694156582</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2577521899608216</v>
+        <v>0.1768418593365303</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2415937040744993</v>
+        <v>0.3078938447096166</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1956796999812876</v>
+        <v>0.3323372001661206</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2506777150115004</v>
+        <v>0.216760436439679</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2829029846773811</v>
+        <v>0.4288386805601746</v>
       </c>
       <c r="U24" t="n">
-        <v>0.310374174802984</v>
+        <v>0.2796983507251078</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5560603124835647</v>
+        <v>0.2633036921867235</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2135036587938169</v>
+        <v>0.1522514072717411</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.4523713206439202</v>
+        <v>0.2932753399242283</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.2124852961994549</v>
+        <v>0.3788023754665158</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.1284523831655429</v>
+        <v>0.2203349900023497</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2483437339261779</v>
+        <v>0.1932017656789343</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.2901322314731292</v>
+        <v>0.1428304767687566</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.3150394957448833</v>
+        <v>0.2578306049734</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.2970586176410723</v>
+        <v>0.1325348784161024</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.273141154820545</v>
+        <v>0.251412553139308</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.2969936035041219</v>
+        <v>0.3180976537222359</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.2703097602466639</v>
+        <v>0.178949934419972</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.24533379761371</v>
+        <v>0.2419929200076593</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.2125131200688856</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0.3517769789420765</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0.6870340672166069</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0.2835631069805937</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0.3672583794529648</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0.2245965179656379</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.3088871501383963</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.2887781978469018</v>
+        <v>0.1779726100687255</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.534711486614373</v>
+        <v>0.4127816246583579</v>
       </c>
       <c r="C25" t="n">
-        <v>0.557609006176916</v>
+        <v>0.4513670273423105</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4004051780851396</v>
+        <v>0.3496938644575716</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5457971026999097</v>
+        <v>0.2364328833614385</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5409638925321981</v>
+        <v>0.3203476338375398</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3994791356457655</v>
+        <v>0.4782234824431362</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3312914291137389</v>
+        <v>0.3325222714115795</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4431268165185223</v>
+        <v>0.5109749094858135</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5932065221301239</v>
+        <v>0.3124822916822513</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3873269193617946</v>
+        <v>0.2034263921640788</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4000375895494668</v>
+        <v>0.2871812531163396</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4732715740554824</v>
+        <v>0.4245820726160768</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5465009326320198</v>
+        <v>0.3188256286398068</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4828205814514998</v>
+        <v>0.3795498872837161</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5553347324974152</v>
+        <v>0.3651801723336197</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5131993728420714</v>
+        <v>0.270461537863202</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4047166276668345</v>
+        <v>0.3140776100745333</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4114742838577523</v>
+        <v>0.282838223275526</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4903354286097076</v>
+        <v>0.5419067788466096</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6695244960013363</v>
+        <v>0.2340191142161165</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3562044888235915</v>
+        <v>0.3351097203461968</v>
       </c>
       <c r="W25" t="n">
-        <v>0.4900275855011309</v>
+        <v>0.2061076521856845</v>
       </c>
       <c r="X25" t="n">
-        <v>0.4523713206439202</v>
+        <v>0.2932753399242283</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.4296829655632335</v>
+        <v>0.2481127058114879</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.3930168999410514</v>
+        <v>0.3552432845698589</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.5017399673222322</v>
+        <v>0.2155156027679093</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.4987063506933438</v>
+        <v>0.3189567168690861</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.5821320303067371</v>
+        <v>0.3536434346352996</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.5016744947838292</v>
+        <v>0.3002210464014208</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.5665865413468534</v>
+        <v>0.3929088345087537</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.5767962720029119</v>
+        <v>0.2168105536799102</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.5069878513931042</v>
+        <v>0.2720908247699894</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.5512942283708838</v>
+        <v>0.3799934180401332</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.4556783177465128</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0.5841635414882923</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.4876620926620991</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0.6718116620757019</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0.4693764409951174</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.6219693403805958</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.5600619419459919</v>
+        <v>0.2662298454994897</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4383084249162878</v>
+        <v>0.4659747179501191</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2982861175313762</v>
+        <v>0.4625161201541372</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4109342969463929</v>
+        <v>0.3808059118820377</v>
       </c>
       <c r="E26" t="n">
-        <v>0.385802339735325</v>
+        <v>0.2961584188674887</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2659356477129398</v>
+        <v>0.35069858793076</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1771629897004359</v>
+        <v>0.4516554903399846</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4364103978262921</v>
+        <v>0.3358463403150813</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3718358242984632</v>
+        <v>0.4452759598873044</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3469846996856064</v>
+        <v>0.3589383577746276</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1635080678383613</v>
+        <v>0.3453141743960039</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3676392803492771</v>
+        <v>0.3013003848172541</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2931169136921485</v>
+        <v>0.4422793241262977</v>
       </c>
       <c r="N26" t="n">
-        <v>0.244933003448704</v>
+        <v>0.3999566664363042</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2350619597351292</v>
+        <v>0.3190946878008364</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3850821600559948</v>
+        <v>0.3963523643399152</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2682172587295527</v>
+        <v>0.2407168142818222</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3064434835588242</v>
+        <v>0.2412572264096745</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2751493417912679</v>
+        <v>0.3204378079517</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3124124749183476</v>
+        <v>0.5389900353968659</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3750191068880135</v>
+        <v>0.29685964507701</v>
       </c>
       <c r="V26" t="n">
-        <v>0.4790356645298458</v>
+        <v>0.2946738537145007</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2303151494725369</v>
+        <v>0.3256157915855947</v>
       </c>
       <c r="X26" t="n">
-        <v>0.2124852961994549</v>
+        <v>0.3788023754665158</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.4296829655632335</v>
+        <v>0.2481127058114879</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.1856424632014325</v>
+        <v>0.4007960651611932</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.2243784470980311</v>
+        <v>0.3270315835243708</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.314096126186407</v>
+        <v>0.4294541153928728</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.2742361555313055</v>
+        <v>0.4420853977530852</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.249496402611939</v>
+        <v>0.3771382420180406</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.3559763605909765</v>
+        <v>0.4226155606200684</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.2774645930491605</v>
+        <v>0.3827864730622021</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.3698593421805308</v>
+        <v>0.3631911766104776</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.3012950426188472</v>
+        <v>0.438806880608748</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.2281543845734533</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0.4483239776466784</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0.6757075308421705</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0.229382376170267</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0.4001436653011263</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0.1480280937497674</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0.4112305702910467</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0.3290960281358035</v>
+        <v>0.3346619851658696</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4132117330767075</v>
+        <v>0.314116613831922</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2527916233891053</v>
+        <v>0.3182811295439305</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3383231471024534</v>
+        <v>0.1877462790026971</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3642972418560868</v>
+        <v>0.1977752315198593</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2986432942397962</v>
+        <v>0.2548520923431914</v>
       </c>
       <c r="G27" t="n">
-        <v>0.157915469238131</v>
+        <v>0.3095085408705507</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3772695121329084</v>
+        <v>0.3175824090963201</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3162142876268748</v>
+        <v>0.4158070103921356</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4133035840967512</v>
+        <v>0.2427520961586564</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1202321507430047</v>
+        <v>0.2260787600462652</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3211549153524123</v>
+        <v>0.2270727433005399</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3073424219506963</v>
+        <v>0.1311562763729155</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3030575264577114</v>
+        <v>0.2369121076069145</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2424764878796981</v>
+        <v>0.2605796191359893</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3267058910351817</v>
+        <v>0.3164432950214119</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.2999912038583119</v>
+        <v>0.2865440452204629</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1824876844721048</v>
+        <v>0.3070411406148059</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2391853678590214</v>
+        <v>0.1989890170841504</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2948960494433945</v>
+        <v>0.5182368376404581</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3810468844810351</v>
+        <v>0.3286184902442067</v>
       </c>
       <c r="V27" t="n">
-        <v>0.491373584012431</v>
+        <v>0.3230248279726515</v>
       </c>
       <c r="W27" t="n">
-        <v>0.2049151572628783</v>
+        <v>0.2303116708808337</v>
       </c>
       <c r="X27" t="n">
-        <v>0.1284523831655429</v>
+        <v>0.2203349900023497</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.3930168999410514</v>
+        <v>0.3552432845698589</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.1856424632014325</v>
+        <v>0.4007960651611932</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.2815297187109832</v>
+        <v>0.2157385558656046</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.3183347204794485</v>
+        <v>0.3074779226551289</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.3547527170942238</v>
+        <v>0.18845694321344</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.2852197587124459</v>
+        <v>0.2418024517603411</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.3216727836386512</v>
+        <v>0.3161419885311681</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.3117998406222879</v>
+        <v>0.4037131773674129</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.3253810076845067</v>
+        <v>0.2682313760998478</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.3103744158037691</v>
+        <v>0.1618453113076788</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.2345647432251881</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0.417845568450034</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0.7325921032894358</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0.2762099225155471</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0.4151031031973113</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0.2404508608371229</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0.3799549015928347</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.3308546149979751</v>
+        <v>0.2235683444395996</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2715240855395805</v>
+        <v>0.3235847926971672</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2945398534646176</v>
+        <v>0.3356637897293322</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3441175683383909</v>
+        <v>0.2366461367886144</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2620492424092982</v>
+        <v>0.1504047877106653</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1977101063296139</v>
+        <v>0.2155285551068835</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2531197814030105</v>
+        <v>0.3907446173664889</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4346214844121113</v>
+        <v>0.2756137849419807</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3587184311389142</v>
+        <v>0.4438046579377176</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2413065612270026</v>
+        <v>0.2386590613897018</v>
       </c>
       <c r="K28" t="n">
-        <v>0.23490564641881</v>
+        <v>0.1144677980255647</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3675051492093114</v>
+        <v>0.2482888307606567</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2236488566201493</v>
+        <v>0.271934170363202</v>
       </c>
       <c r="N28" t="n">
-        <v>0.1151007954285409</v>
+        <v>0.2031001409225986</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1872440773633686</v>
+        <v>0.2755389364395295</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3041155606027348</v>
+        <v>0.2850450047992735</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.110819558083858</v>
+        <v>0.2336628585536174</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3052126415154512</v>
+        <v>0.2801567595235592</v>
       </c>
       <c r="S28" t="n">
-        <v>0.261485730875094</v>
+        <v>0.1920489559368984</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2545333145138796</v>
+        <v>0.456279646593099</v>
       </c>
       <c r="U28" t="n">
-        <v>0.3353739079332042</v>
+        <v>0.203440816658389</v>
       </c>
       <c r="V28" t="n">
-        <v>0.5768619701795289</v>
+        <v>0.2690591413436109</v>
       </c>
       <c r="W28" t="n">
-        <v>0.3004998171987503</v>
+        <v>0.1096737601944663</v>
       </c>
       <c r="X28" t="n">
-        <v>0.2483437339261779</v>
+        <v>0.1932017656789343</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5017399673222322</v>
+        <v>0.2155156027679093</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.2243784470980311</v>
+        <v>0.3270315835243708</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.2815297187109832</v>
+        <v>0.2157385558656046</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.1636930185965497</v>
+        <v>0.2450838245416885</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.1530059594877929</v>
+        <v>0.2282220185136468</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.2397855999166776</v>
+        <v>0.1999710477752269</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.2819562814805098</v>
+        <v>0.3543247193796392</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.1896653112125309</v>
+        <v>0.2415283298410782</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.2367380583350213</v>
+        <v>0.2018477031139391</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.1409292827705453</v>
+        <v>0.2512435175904262</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.1851102747163547</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0.3018179089256301</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0.6647079248395101</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0.2983103710466889</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0.3126546569980899</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0.2209097697498799</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.2966384205216572</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.2037611547533631</v>
+        <v>0.1918482484894319</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1611444284299403</v>
+        <v>0.1861819481701183</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3123404618789838</v>
+        <v>0.2321450678231125</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2462335822360572</v>
+        <v>0.2139888543473405</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1547323935242761</v>
+        <v>0.2445039186425954</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2270511528876104</v>
+        <v>0.2804309971073917</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2428667572188161</v>
+        <v>0.3426959890762116</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4374551282382673</v>
+        <v>0.3095924912919123</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2736182420158469</v>
+        <v>0.4287793197201197</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2400440558748673</v>
+        <v>0.246818431803476</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2585646523704642</v>
+        <v>0.250239835696435</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3101361068043093</v>
+        <v>0.2936329084251146</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1516761134086641</v>
+        <v>0.3058007698738928</v>
       </c>
       <c r="N29" t="n">
-        <v>0.1886686464263574</v>
+        <v>0.3308980689049165</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1690594872972605</v>
+        <v>0.3439665193207485</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2368239230019384</v>
+        <v>0.2560714758662188</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1859745577497603</v>
+        <v>0.3600896475511293</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2987065171370876</v>
+        <v>0.4140185202139181</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2365923136771954</v>
+        <v>0.3099324041488422</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3138389917979056</v>
+        <v>0.4302504296636231</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3442764590800131</v>
+        <v>0.3512818991942925</v>
       </c>
       <c r="V29" t="n">
-        <v>0.5854347936783967</v>
+        <v>0.3505643942092199</v>
       </c>
       <c r="W29" t="n">
-        <v>0.3345660036733711</v>
+        <v>0.2214808775873784</v>
       </c>
       <c r="X29" t="n">
-        <v>0.2901322314731292</v>
+        <v>0.1428304767687566</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.4987063506933438</v>
+        <v>0.3189567168690861</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.314096126186407</v>
+        <v>0.4294541153928728</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.3183347204794485</v>
+        <v>0.3074779226551289</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.1636930185965497</v>
+        <v>0.2450838245416885</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.266458522736406</v>
+        <v>0.3114764916229127</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.2997478713462896</v>
+        <v>0.2092076281085279</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.2360372951329607</v>
+        <v>0.2313207656418144</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2171940834053949</v>
+        <v>0.337274371060753</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.2100546775871128</v>
+        <v>0.2558896004998304</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.1577725228369254</v>
+        <v>0.2703595752470713</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.1482454517983402</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0.2232011456977394</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0.7612864372785064</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.406227391203811</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0.3394455077830402</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0.3101201165848129</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.242257972496721</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.1799938242504201</v>
+        <v>0.2109342421480452</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3382980497797735</v>
+        <v>0.3620940229625715</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3406378610909753</v>
+        <v>0.3679654603517222</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4438717894013525</v>
+        <v>0.270120746795449</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3124573061015185</v>
+        <v>0.2089277061201505</v>
       </c>
       <c r="F30" t="n">
-        <v>0.181730913428489</v>
+        <v>0.3015554053040126</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3368240115597659</v>
+        <v>0.3657995330222239</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4877275043974274</v>
+        <v>0.3543358226048736</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4607590640620282</v>
+        <v>0.4271854950494071</v>
       </c>
       <c r="J30" t="n">
-        <v>0.284973432918567</v>
+        <v>0.2754525613902492</v>
       </c>
       <c r="K30" t="n">
-        <v>0.3367874327373435</v>
+        <v>0.1990854782380168</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4802720233502358</v>
+        <v>0.311908412843902</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2927582696240481</v>
+        <v>0.2620596493976464</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1062657869119027</v>
+        <v>0.2231507160273779</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2710524352564069</v>
+        <v>0.3657031785604838</v>
       </c>
       <c r="P30" t="n">
-        <v>0.3573501051044435</v>
+        <v>0.3166767993235384</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1569041688143598</v>
+        <v>0.3539858620774821</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3697362932547953</v>
+        <v>0.3689316399724785</v>
       </c>
       <c r="S30" t="n">
-        <v>0.3880062832819917</v>
+        <v>0.2725155389985139</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2379864999940971</v>
+        <v>0.51933577976279</v>
       </c>
       <c r="U30" t="n">
-        <v>0.355597216572326</v>
+        <v>0.3032168782242811</v>
       </c>
       <c r="V30" t="n">
-        <v>0.6597791385364855</v>
+        <v>0.3807600005363621</v>
       </c>
       <c r="W30" t="n">
-        <v>0.3352668188034546</v>
+        <v>0.2105293120693882</v>
       </c>
       <c r="X30" t="n">
-        <v>0.3150394957448833</v>
+        <v>0.2578306049734</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5821320303067371</v>
+        <v>0.3536434346352996</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.2742361555313055</v>
+        <v>0.4420853977530852</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.3547527170942238</v>
+        <v>0.18845694321344</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.1530059594877929</v>
+        <v>0.2282220185136468</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.266458522736406</v>
+        <v>0.3114764916229127</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.2109720150889753</v>
+        <v>0.2059398696072919</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.3226523412128967</v>
+        <v>0.3684820643683778</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.1961262770851434</v>
+        <v>0.3442921391400957</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.3308607116488256</v>
+        <v>0.2236987984722077</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.1959393319851353</v>
+        <v>0.2024590444754477</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.2999095518201637</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0.3410177597221311</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0.6072319347593607</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0.3355062804518619</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0.2534805458693623</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0.2880057556115702</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0.3271698897016359</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0.217416711445048</v>
+        <v>0.2551304070925953</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3774793359873343</v>
+        <v>0.3046194617413157</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3448637947831505</v>
+        <v>0.2676977291597868</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4233632999191592</v>
+        <v>0.2299701983830411</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3332031301469809</v>
+        <v>0.1765609488011675</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2315866362877967</v>
+        <v>0.1654004490593198</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2823384133712276</v>
+        <v>0.2900617150881523</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4500773365293429</v>
+        <v>0.2107960197503087</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4281318005672624</v>
+        <v>0.3396466661682929</v>
       </c>
       <c r="J31" t="n">
-        <v>0.327840193564598</v>
+        <v>0.1396563613514463</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2903615193835818</v>
+        <v>0.1893572594252143</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4333881691294119</v>
+        <v>0.2265040841907006</v>
       </c>
       <c r="M31" t="n">
-        <v>0.257017643359763</v>
+        <v>0.2886134161636775</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1993915889238514</v>
+        <v>0.2944524973464878</v>
       </c>
       <c r="O31" t="n">
-        <v>0.2783962922543017</v>
+        <v>0.3199132722385548</v>
       </c>
       <c r="P31" t="n">
-        <v>0.373997417730279</v>
+        <v>0.1513124620332173</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2546827134241861</v>
+        <v>0.3315889110613328</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3122924100575596</v>
+        <v>0.3072406552176908</v>
       </c>
       <c r="S31" t="n">
-        <v>0.3651425952731092</v>
+        <v>0.2403229887216632</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1936700557149172</v>
+        <v>0.4327022459340723</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4052201491093693</v>
+        <v>0.2341449059515845</v>
       </c>
       <c r="V31" t="n">
-        <v>0.600631889567089</v>
+        <v>0.2779009940098109</v>
       </c>
       <c r="W31" t="n">
-        <v>0.268491223373315</v>
+        <v>0.1552219888380412</v>
       </c>
       <c r="X31" t="n">
-        <v>0.2970586176410723</v>
+        <v>0.1325348784161024</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5016744947838292</v>
+        <v>0.3002210464014208</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.249496402611939</v>
+        <v>0.3771382420180406</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.2852197587124459</v>
+        <v>0.2418024517603411</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.2397855999166776</v>
+        <v>0.1999710477752269</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.2997478713462896</v>
+        <v>0.2092076281085279</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.2109720150889753</v>
+        <v>0.2059398696072919</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.3566221778731629</v>
+        <v>0.3164513462337706</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.2583418300350703</v>
+        <v>0.289546144440204</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.3903437524657789</v>
+        <v>0.1152283667923853</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.2915218351191312</v>
+        <v>0.2602468718988838</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.3108121391843984</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.3806140973928959</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0.6797879460023686</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.3445078950474844</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0.3406978068739125</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0.3292683452495166</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.3794973450262299</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.2881884241897373</v>
+        <v>0.2295138163818386</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2869246775107943</v>
+        <v>0.1565094563156229</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2169808890681555</v>
+        <v>0.2580213922664524</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3209167797192633</v>
+        <v>0.1707344096158784</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1640426538923894</v>
+        <v>0.2654839942164366</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2045440901289942</v>
+        <v>0.3839217956449147</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2696569355149389</v>
+        <v>0.3120253084986568</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4284740431420084</v>
+        <v>0.402490866130974</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3321445358818296</v>
+        <v>0.4372812722741581</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3786385332900696</v>
+        <v>0.3232800799654633</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3249573634445214</v>
+        <v>0.3418422981571004</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4157136601373941</v>
+        <v>0.3147907625132514</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2464355140252383</v>
+        <v>0.2851140986416889</v>
       </c>
       <c r="N32" t="n">
-        <v>0.272346704366664</v>
+        <v>0.3858148657342722</v>
       </c>
       <c r="O32" t="n">
-        <v>0.2044983041306346</v>
+        <v>0.3469502433990936</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1171677869939665</v>
+        <v>0.3613739903776846</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2464303393933069</v>
+        <v>0.3852659046310177</v>
       </c>
       <c r="R32" t="n">
-        <v>0.2629511725859354</v>
+        <v>0.4467056309920243</v>
       </c>
       <c r="S32" t="n">
-        <v>0.3607241389361425</v>
+        <v>0.3848524562881842</v>
       </c>
       <c r="T32" t="n">
-        <v>0.3171854728831933</v>
+        <v>0.538842557744599</v>
       </c>
       <c r="U32" t="n">
-        <v>0.2671966296816718</v>
+        <v>0.4630810604728939</v>
       </c>
       <c r="V32" t="n">
-        <v>0.6862224498642454</v>
+        <v>0.4247586323691462</v>
       </c>
       <c r="W32" t="n">
-        <v>0.2860879798154172</v>
+        <v>0.3229743997733477</v>
       </c>
       <c r="X32" t="n">
-        <v>0.273141154820545</v>
+        <v>0.251412553139308</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.5665865413468534</v>
+        <v>0.3929088345087537</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.3559763605909765</v>
+        <v>0.4226155606200684</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.3216727836386512</v>
+        <v>0.3161419885311681</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2819562814805098</v>
+        <v>0.3543247193796392</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.2360372951329607</v>
+        <v>0.2313207656418144</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.3226523412128967</v>
+        <v>0.3684820643683778</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.3566221778731629</v>
+        <v>0.3164513462337706</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.2114728715237563</v>
+        <v>0.4865432931484636</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.3032244441368258</v>
+        <v>0.3589259167130799</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.1792365261289854</v>
+        <v>0.2421659799035956</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.2465200191892821</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0.2452225647553178</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0.7725743513497924</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.4830738832028991</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0.2824779079589276</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0.3632343788685834</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.1282573516446931</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.173268612450154</v>
+        <v>0.2039183074467407</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3136262933685272</v>
+        <v>0.4566797376786071</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2878997214712728</v>
+        <v>0.4681113610637689</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3929247145358267</v>
+        <v>0.424540880590208</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2545807807437642</v>
+        <v>0.3132287375169506</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1968388127013928</v>
+        <v>0.312666672915825</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2744717879729855</v>
+        <v>0.5051795036298905</v>
       </c>
       <c r="H33" t="n">
-        <v>0.454403546636226</v>
+        <v>0.3237489535876773</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3831847160328181</v>
+        <v>0.5024441308808834</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2947456163018362</v>
+        <v>0.3466441231576973</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3019984364084913</v>
+        <v>0.2243420539475923</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4149813512023821</v>
+        <v>0.3630878678236224</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2333511689069191</v>
+        <v>0.4692312641972033</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1597987648806432</v>
+        <v>0.3200356248880099</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2370359622758108</v>
+        <v>0.4338261063383205</v>
       </c>
       <c r="P33" t="n">
-        <v>0.2871337624947748</v>
+        <v>0.3358993760640132</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.212716647756272</v>
+        <v>0.3608730394837131</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3211812495919816</v>
+        <v>0.3708334269410775</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3411455949910237</v>
+        <v>0.3149377175302987</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2843246247454799</v>
+        <v>0.4778764466037598</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2931429836690956</v>
+        <v>0.1938572196956187</v>
       </c>
       <c r="V33" t="n">
-        <v>0.6408527500479861</v>
+        <v>0.3362986542964774</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2857283193787624</v>
+        <v>0.2238325729223176</v>
       </c>
       <c r="X33" t="n">
-        <v>0.2969936035041219</v>
+        <v>0.3180976537222359</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.5767962720029119</v>
+        <v>0.2168105536799102</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2774645930491605</v>
+        <v>0.3827864730622021</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.3117998406222879</v>
+        <v>0.4037131773674129</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1896653112125309</v>
+        <v>0.2415283298410782</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.2171940834053949</v>
+        <v>0.337274371060753</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.1961262770851434</v>
+        <v>0.3442921391400957</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.2583418300350703</v>
+        <v>0.289546144440204</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.2114728715237563</v>
+        <v>0.4865432931484636</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.3212876279538053</v>
+        <v>0.2348169337786485</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.1772772647151498</v>
+        <v>0.4382045603415631</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.2433793178564067</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0.3233337831018624</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0.725612763302579</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.3925059826987143</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0.2466382588749047</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0.3071125786189795</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.2578428187732601</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.1567251211474222</v>
+        <v>0.3506692717389396</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.216139547794732</v>
+        <v>0.3388028580878903</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3406959276128624</v>
+        <v>0.3375205849514797</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2565369289025155</v>
+        <v>0.2878125083453043</v>
       </c>
       <c r="E34" t="n">
-        <v>0.26933875815011</v>
+        <v>0.1977769808344637</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2940922097177937</v>
+        <v>0.1915242751212803</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3229621662024001</v>
+        <v>0.3469741861582016</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4316282625884242</v>
+        <v>0.2357530514192114</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3349507309513756</v>
+        <v>0.380311714929703</v>
       </c>
       <c r="J34" t="n">
-        <v>0.3553873301078261</v>
+        <v>0.2127553642329386</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2953882293207462</v>
+        <v>0.1543913568233148</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3711795891662545</v>
+        <v>0.2419380223010046</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3277760889909939</v>
+        <v>0.329432727257408</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2706653342670165</v>
+        <v>0.2607160018338174</v>
       </c>
       <c r="O34" t="n">
-        <v>0.2581445800081346</v>
+        <v>0.3501974904777392</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2756172666041503</v>
+        <v>0.2025723347783263</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2150443012987401</v>
+        <v>0.337487170711645</v>
       </c>
       <c r="R34" t="n">
-        <v>0.3000943395384623</v>
+        <v>0.3083302830246252</v>
       </c>
       <c r="S34" t="n">
-        <v>0.2718714238986559</v>
+        <v>0.2463875544711105</v>
       </c>
       <c r="T34" t="n">
-        <v>0.354592809618933</v>
+        <v>0.4743543462246376</v>
       </c>
       <c r="U34" t="n">
-        <v>0.3912459109001518</v>
+        <v>0.2059943641364465</v>
       </c>
       <c r="V34" t="n">
-        <v>0.6059704413486603</v>
+        <v>0.2778509324306785</v>
       </c>
       <c r="W34" t="n">
-        <v>0.409916400718198</v>
+        <v>0.1415728339178221</v>
       </c>
       <c r="X34" t="n">
-        <v>0.2703097602466639</v>
+        <v>0.178949934419972</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.5069878513931042</v>
+        <v>0.2720908247699894</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.3698593421805308</v>
+        <v>0.3631911766104776</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.3253810076845067</v>
+        <v>0.2682313760998478</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.2367380583350213</v>
+        <v>0.2018477031139391</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.2100546775871128</v>
+        <v>0.2558896004998304</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.3308607116488256</v>
+        <v>0.2236987984722077</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.3903437524657789</v>
+        <v>0.1152283667923853</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.3032244441368258</v>
+        <v>0.3589259167130799</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.3212876279538053</v>
+        <v>0.2348169337786485</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.2054148165834482</v>
+        <v>0.3062338229470688</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.2334632581856722</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0.2666635664292168</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0.7249809149335342</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.3702559877560458</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0.350567099017814</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0.3109362316825049</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.2979460722253684</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.2429125908212942</v>
+        <v>0.2478298037484245</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.2193068745582441</v>
+        <v>0.2500640977011001</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2539300538288434</v>
+        <v>0.3010666876846366</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3177593489337315</v>
+        <v>0.1386477974872029</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1744319253517568</v>
+        <v>0.1965699711241716</v>
       </c>
       <c r="F35" t="n">
-        <v>0.14495595835128</v>
+        <v>0.3307230944399311</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2757389955224818</v>
+        <v>0.3421131223762436</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4405301473187531</v>
+        <v>0.3927348255203867</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3561236736898169</v>
+        <v>0.4596402033607281</v>
       </c>
       <c r="J35" t="n">
-        <v>0.289665966575825</v>
+        <v>0.2868600540121342</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2870980172465573</v>
+        <v>0.2547189410401388</v>
       </c>
       <c r="L35" t="n">
-        <v>0.408770764524723</v>
+        <v>0.3018349840698071</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2383959462137812</v>
+        <v>0.1577740962322733</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1469154529729303</v>
+        <v>0.2660382563401724</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1683926080566518</v>
+        <v>0.3207444093340364</v>
       </c>
       <c r="P35" t="n">
-        <v>0.1974899975122066</v>
+        <v>0.3599671172658837</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.09443094600793056</v>
+        <v>0.3425174267975587</v>
       </c>
       <c r="R35" t="n">
-        <v>0.2833912761296503</v>
+        <v>0.3932125257282984</v>
       </c>
       <c r="S35" t="n">
-        <v>0.3155749260440156</v>
+        <v>0.3130694637664324</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2622437538190898</v>
+        <v>0.5398244413442074</v>
       </c>
       <c r="U35" t="n">
-        <v>0.2874531655190166</v>
+        <v>0.3975474913946244</v>
       </c>
       <c r="V35" t="n">
-        <v>0.6589201771553191</v>
+        <v>0.4051857334215047</v>
       </c>
       <c r="W35" t="n">
-        <v>0.3131983666267604</v>
+        <v>0.2601207231419383</v>
       </c>
       <c r="X35" t="n">
-        <v>0.24533379761371</v>
+        <v>0.2419929200076593</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.5512942283708838</v>
+        <v>0.3799934180401332</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.3012950426188472</v>
+        <v>0.438806880608748</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.3103744158037691</v>
+        <v>0.1618453113076788</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.1409292827705453</v>
+        <v>0.2512435175904262</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.1577725228369254</v>
+        <v>0.2703595752470713</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.1959393319851353</v>
+        <v>0.2024590444754477</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.2915218351191312</v>
+        <v>0.2602468718988838</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.1792365261289854</v>
+        <v>0.2421659799035956</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.1772772647151498</v>
+        <v>0.4382045603415631</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.2054148165834482</v>
+        <v>0.3062338229470688</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.202752267028271</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.2071887429013688</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0.6890348300410782</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0.3846718559117389</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0.2391920620075497</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0.2847990530714284</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.1766901568875255</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.1153942436422338</v>
+        <v>0.186624237683293</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.2858124149065213</v>
+        <v>0.2054683227824581</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2594059147514446</v>
+        <v>0.2901962612063297</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2553521665087906</v>
+        <v>0.135841523652509</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2347955839344378</v>
+        <v>0.1058450470449592</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2315229413152039</v>
+        <v>0.3006342508942455</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1393552452425942</v>
+        <v>0.345609306582935</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4408610644882873</v>
+        <v>0.3308297030454014</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2191586470705325</v>
+        <v>0.4295336931374962</v>
       </c>
       <c r="J36" t="n">
-        <v>0.2718911139006169</v>
+        <v>0.2777730236961127</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1557920284559451</v>
+        <v>0.1783481463172394</v>
       </c>
       <c r="L36" t="n">
-        <v>0.264467304943567</v>
+        <v>0.2554258500563629</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1904783415195095</v>
+        <v>0.2397702027888547</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2156668989353693</v>
+        <v>0.2262663055798564</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1083870105543655</v>
+        <v>0.2760331636701563</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2479409044525452</v>
+        <v>0.306761728632114</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2182604499535152</v>
+        <v>0.2696358584746515</v>
       </c>
       <c r="R36" t="n">
-        <v>0.2788974450055725</v>
+        <v>0.3523096826171525</v>
       </c>
       <c r="S36" t="n">
-        <v>0.1663039272707412</v>
+        <v>0.2717710195933907</v>
       </c>
       <c r="T36" t="n">
-        <v>0.3487808285335481</v>
+        <v>0.4915108850606058</v>
       </c>
       <c r="U36" t="n">
-        <v>0.3139496900970591</v>
+        <v>0.3196542408505018</v>
       </c>
       <c r="V36" t="n">
-        <v>0.5148616037469794</v>
+        <v>0.3303726993054028</v>
       </c>
       <c r="W36" t="n">
-        <v>0.2827334233821683</v>
+        <v>0.1589490098208889</v>
       </c>
       <c r="X36" t="n">
-        <v>0.2125131200688856</v>
+        <v>0.1779726100687255</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.4556783177465128</v>
+        <v>0.2662298454994897</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.2281543845734533</v>
+        <v>0.3346619851658696</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.2345647432251881</v>
+        <v>0.2235683444395996</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.1851102747163547</v>
+        <v>0.1918482484894319</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.1482454517983402</v>
+        <v>0.2109342421480452</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.2999095518201637</v>
+        <v>0.2551304070925953</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.3108121391843984</v>
+        <v>0.2295138163818386</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.2465200191892821</v>
+        <v>0.2039183074467407</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.2433793178564067</v>
+        <v>0.3506692717389396</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.2334632581856722</v>
+        <v>0.2478298037484245</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.202752267028271</v>
+        <v>0.186624237683293</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0.3106995974431362</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0.7527141836603837</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0.335868242718715</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0.362669824016138</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0.2100623802776198</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0.2849277178451471</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0.2352253684450607</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0.1599345305495599</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.3367235115124469</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.2864574008643716</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.1371479720446589</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.26371747713521</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.3725966430942491</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.4938900342880537</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.3662758907675144</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.3394653398630165</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.3918690267233366</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.4370029314465217</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.2857520503096467</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.2944623851594366</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.2609657311555733</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.1887781816972272</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.2505674264817183</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.3364848871532977</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.3889987239186525</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.3330052073194309</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.3635246287155983</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.7232979270857065</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.4037120803673644</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.3517769789420765</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0.5841635414882923</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0.4483239776466784</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.417845568450034</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.3018179089256301</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.2232011456977394</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.3410177597221311</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.3806140973928959</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.2452225647553178</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.3233337831018624</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.2666635664292168</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.2071887429013688</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.3106995974431362</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0.7405687577698784</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.5219807186333136</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0.3321650767765615</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0.4417334051685986</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.1733425960263157</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.2287848053551713</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0.7812048733065775</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.6961803443665078</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.8325546111576978</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.7777991260419098</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.6841661877711658</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.7694155380506558</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.6830843423018097</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.7339719654015158</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.7855226121195802</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.6625376626544052</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.7206586284775655</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.7658615029982968</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.6596625842296384</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.7706425957871538</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0.7695198560805719</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0.6765377254040345</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.6801090539016454</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.7201539425277855</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.6870340672166069</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0.8325546111576977</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0.6757075308421705</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.7325921032894358</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.6647079248395101</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.7612864372785064</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.6072319347593607</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.6797879460023686</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.7725743513497924</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.725612763302579</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.7249809149335342</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.6890348300410782</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.7527141836603837</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0.7405687577698784</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.5829224882261884</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0.6667044142408133</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0.6502387678692824</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.7398356376060425</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.7364242778222</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.5014959369649594</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.3933408718232482</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.4820203983786536</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.4985584931250037</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.3854593817615485</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.3384774576731563</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.5214502029138955</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.4525730861764261</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.4015255323802023</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.2648015290392599</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.4260807810402555</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.4398060125844658</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.3210300798750583</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.3601240817628735</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.4890704623309902</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.3451287608700729</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0.4053461000607541</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.321125352750404</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0.3989539263810629</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.447773250086628</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.4734574377492569</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0.3772939960724236</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.2835631069805937</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0.4876620926620991</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0.229382376170267</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.2762099225155471</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.2983103710466889</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.406227391203811</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.3355062804518619</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0.3445078950474844</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0.4830738832028991</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.3925059826987143</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0.3702559877560458</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.3846718559117389</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.335868242718715</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0.5219807186333136</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0.5829224882261884</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0.4458195246839185</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0.1967902252497741</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.5056892261273613</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.42626850487259</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Uganda</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.3657642261553331</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.3664967466749209</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.4692898071968737</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.3171315793244604</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.2189481565163989</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.4010132861305519</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.5395348268068524</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.4982125687883669</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.4031437948588085</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.4281371796033307</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.56203626390631</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.3927497614230813</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.2349961211140964</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0.3304434899278499</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.321057201007127</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0.262994007298524</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.4020600942911589</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0.4803650487846528</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0.344543231116638</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0.3554094072020421</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0.7612864372785065</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.4105073156227491</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.3672583794529648</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0.6718116620757019</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0.4001436653011263</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.4151031031973113</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.3126546569980899</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0.3394455077830402</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.2534805458693623</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.3406978068739125</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.2824779079589276</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.2466382588749047</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0.350567099017814</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0.2391920620075497</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.362669824016138</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0.3321650767765615</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0.6667044142408133</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.4458195246839185</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0.3779589221230635</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.2786276526892044</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0.1967595610805419</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0.4281790522358774</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.3101215835059233</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.4046124920473814</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.3930004818450624</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.2806333352377638</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.2297636297043361</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.4754268669166877</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.3721323822820192</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.3414339010040642</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.2013379584309059</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.3840038626906518</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.340641455368389</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.2503882224809887</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.2368961961518657</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0.3823178671118937</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.2557558953387334</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.3489478498041539</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0.2723577801231682</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0.3733814292209105</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0.3683676032520843</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0.4940641360161619</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0.3113680858439996</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0.2245965179656379</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0.4693764409951174</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0.1480280937497674</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.2404508608371229</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.2209097697498799</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0.3101201165848129</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.2880057556115702</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0.3292683452495166</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.3632343788685834</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.3071125786189795</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0.3109362316825049</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0.2847990530714284</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0.2100623802776198</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0.4417334051685986</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0.6502387678692824</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0.1967902252497741</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0.3779589221230635</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0.4059604134233779</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.3281142679643047</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0.2600279882612592</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.2353246010605236</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.3437758518575662</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.1472318949544184</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.2286624029848918</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.3353345301061202</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.5043557289649575</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.3602270195424285</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.3555585207807144</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.3694877950117928</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.4452210869874537</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.2810172913006456</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.2810390671408994</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.2275848286563561</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.1075492301261601</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.256449520662638</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.320685064849072</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.3870290496972799</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.3397281741180733</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.2466722306350327</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.7310069145300502</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.3360798405474507</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.3088871501383963</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0.6219693403805958</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0.4112305702910467</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.3799549015928347</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.2966384205216572</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.242257972496721</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.3271698897016359</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.3794973450262299</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.1282573516446931</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.2578428187732601</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0.2979460722253684</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0.1766901568875255</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.2849277178451471</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0.1733425960263157</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0.7398356376060425</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.5056892261273613</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0.2786276526892044</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0.4059604134233779</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.2007291654354955</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>United States of America</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.2196147769685995</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.3070745460078571</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.3253913436534809</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.1713994724079775</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.1375405977880776</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.2854464972108733</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.4257066487753154</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.3759923499814662</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.3310995879994968</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.3216629530074162</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.4362331980695221</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.243600129768574</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.1589464533120713</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0.2151318758603338</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0.216089682725531</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.1538581827981373</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.2881792163590601</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.3574078085119932</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0.2688398240265304</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0.3334332634662363</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0.6782095932856456</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0.3383193594118835</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.2887781978469018</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0.5600619419459919</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0.3290960281358035</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.3308546149979751</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0.2037611547533631</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0.1799938242504201</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.217416711445048</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0.2881884241897373</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.173268612450154</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.1567251211474222</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.2429125908212942</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0.1153942436422338</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.2352253684450607</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0.2287848053551713</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0.7364242778222</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0.42626850487259</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0.1967595610805419</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0.3281142679643047</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.2007291654354955</v>
-      </c>
-      <c r="AQ43" t="n">
         <v>0</v>
       </c>
     </row>
